--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97579</v>
+        <v>97582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96645</v>
+        <v>96648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92060</v>
+        <v>92063</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92060</v>
+        <v>92063</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 30317-2026 artfynd.xlsx
+++ b/artfynd/A 30317-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136037267</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136037315</v>
       </c>
       <c r="B3" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136037006</v>
       </c>
       <c r="B7" t="n">
-        <v>96648</v>
+        <v>96649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>136038484</v>
       </c>
       <c r="B9" t="n">
-        <v>92063</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>136075610</v>
       </c>
       <c r="B10" t="n">
-        <v>92063</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
